--- a/UPAutomationFramework/src/main/resources/ForestDetails.xlsx
+++ b/UPAutomationFramework/src/main/resources/ForestDetails.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationFramework\UPERPAutomationWithPawan\ReadFromExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationFramework\UPAutomationFramework\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCFA0EC-9F24-4879-99E3-A2CA41DB697C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFEDCBB-F9E7-4E18-A71D-0270CFFEFF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="20415" windowHeight="8745" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="4" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="922">
   <si>
     <t>code</t>
   </si>
@@ -2780,16 +2780,29 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Valid</t>
-  </si>
-  <si>
     <t>invalid</t>
+  </si>
+  <si>
+    <t>dsmluc</t>
+  </si>
+  <si>
+    <t>rmlko</t>
+  </si>
+  <si>
+    <t>valid</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3174,11 +3187,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EC9CFE-4783-4ABC-A9D7-AE0CC4415A80}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="7" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.5703125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="16.42578125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
@@ -3191,9 +3204,25 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B2" s="7">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>917</v>
+      </c>
+      <c r="B3" s="7">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>918</v>
+      </c>
+      <c r="B4" s="7">
         <v>123456</v>
       </c>
     </row>
@@ -3204,14 +3233,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7401DEBD-ED50-4396-AB95-8C790EF255A9}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.5703125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>907</v>
       </c>
@@ -3221,8 +3250,11 @@
       <c r="C1" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>909</v>
       </c>
@@ -3230,10 +3262,13 @@
         <v>123456</v>
       </c>
       <c r="C2" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>919</v>
+      </c>
+      <c r="D2" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>909</v>
       </c>
@@ -3241,7 +3276,24 @@
         <v>1234567</v>
       </c>
       <c r="C3" t="s">
+        <v>916</v>
+      </c>
+      <c r="D3" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>917</v>
+      </c>
+      <c r="B4" s="7">
+        <v>123456</v>
+      </c>
+      <c r="C4" t="s">
+        <v>919</v>
+      </c>
+      <c r="D4" t="s">
+        <v>921</v>
       </c>
     </row>
   </sheetData>
@@ -3254,9 +3306,9 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="5.28515625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="9.85546875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="9.5703125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3313,9 +3365,9 @@
   <dimension ref="A1:C658"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="16.85546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="18.5703125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="14.0" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -10569,10 +10621,10 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="23.140625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.5703125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="14.140625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="18.85546875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10644,8 +10696,8 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.5703125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.28515625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">

--- a/UPAutomationFramework/src/main/resources/ForestDetails.xlsx
+++ b/UPAutomationFramework/src/main/resources/ForestDetails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationFramework\UPAutomationFramework\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFEDCBB-F9E7-4E18-A71D-0270CFFEFF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B405ADD-C954-497D-914F-BEBBEBA87782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2685" yWindow="2685" windowWidth="20415" windowHeight="8745" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/UPAutomationFramework/src/main/resources/ForestDetails.xlsx
+++ b/UPAutomationFramework/src/main/resources/ForestDetails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationFramework\UPAutomationFramework\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B405ADD-C954-497D-914F-BEBBEBA87782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B5FDA5-B14B-4645-A3E9-3D5691F4CF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="20415" windowHeight="8745" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="4" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2027" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="923">
   <si>
     <t>code</t>
   </si>
@@ -2793,6 +2793,9 @@
   </si>
   <si>
     <t>Result</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>Pass</t>
@@ -2872,7 +2875,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2883,6 +2886,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3206,8 +3212,8 @@
       <c r="A2" t="s">
         <v>909</v>
       </c>
-      <c r="B2" s="7">
-        <v>123456</v>
+      <c r="B2" s="8" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3227,13 +3233,16 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{7D466A77-B8B6-477E-9B7A-9601C969E204}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7401DEBD-ED50-4396-AB95-8C790EF255A9}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="12.5703125" collapsed="true"/>
@@ -3279,7 +3288,7 @@
         <v>916</v>
       </c>
       <c r="D3" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3293,10 +3302,27 @@
         <v>919</v>
       </c>
       <c r="D4" t="s">
-        <v>921</v>
+        <v>922</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>909</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="C5" t="s">
+        <v>919</v>
+      </c>
+      <c r="D5" t="s">
+        <v>922</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{F538DB91-0C3F-4D2E-81D8-67729B4F2F9B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
